--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2018/CALIFORNIA_2018.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2018/CALIFORNIA_2018.xlsx
@@ -1381,7 +1381,7 @@
         <v>24</v>
       </c>
       <c r="D57">
-        <v>9.921947347532743E-05</v>
+        <v>9.921947347532744E-05</v>
       </c>
     </row>
     <row r="58">
@@ -2857,7 +2857,7 @@
         <v>24</v>
       </c>
       <c r="D139">
-        <v>9.921947347532743E-05</v>
+        <v>9.921947347532744E-05</v>
       </c>
     </row>
     <row r="140">
@@ -3613,7 +3613,7 @@
         <v>24</v>
       </c>
       <c r="D181">
-        <v>9.921947347532743E-05</v>
+        <v>9.921947347532744E-05</v>
       </c>
     </row>
     <row r="182">
@@ -4146,7 +4146,7 @@
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>Cuatro Cienegas</t>
+          <t>Cuatrocienegas</t>
         </is>
       </c>
       <c r="C211">
@@ -4783,7 +4783,7 @@
         <v>2363</v>
       </c>
       <c r="D246">
-        <v>0.009768983992591613</v>
+        <v>0.009768983992591612</v>
       </c>
     </row>
     <row r="247">
@@ -5082,7 +5082,7 @@
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>General Simon Bolivar</t>
+          <t>Gral. Simon Bolivar</t>
         </is>
       </c>
       <c r="C263">
@@ -5287,7 +5287,7 @@
         <v>24</v>
       </c>
       <c r="D274">
-        <v>9.921947347532743E-05</v>
+        <v>9.921947347532744E-05</v>
       </c>
     </row>
     <row r="275">
@@ -8070,7 +8070,7 @@
       </c>
       <c r="B429" t="inlineStr">
         <is>
-          <t>Dolores Hidalgo Cuna De La Independencia Nacional</t>
+          <t>Dolores Hidalgo</t>
         </is>
       </c>
       <c r="C429">
@@ -9319,7 +9319,7 @@
         <v>221</v>
       </c>
       <c r="D498">
-        <v>0.0009136459849186401</v>
+        <v>0.00091364598491864</v>
       </c>
     </row>
     <row r="499">
@@ -9535,7 +9535,7 @@
         <v>227</v>
       </c>
       <c r="D510">
-        <v>0.0009384508532874719</v>
+        <v>0.000938450853287472</v>
       </c>
     </row>
     <row r="511">
@@ -13009,7 +13009,7 @@
         <v>24</v>
       </c>
       <c r="D703">
-        <v>9.921947347532743E-05</v>
+        <v>9.921947347532744E-05</v>
       </c>
     </row>
     <row r="704">
@@ -13495,7 +13495,7 @@
         <v>232</v>
       </c>
       <c r="D730">
-        <v>0.0009591215769281651</v>
+        <v>0.0009591215769281652</v>
       </c>
     </row>
     <row r="731">
@@ -16123,7 +16123,7 @@
         <v>227</v>
       </c>
       <c r="D876">
-        <v>0.0009384508532874719</v>
+        <v>0.000938450853287472</v>
       </c>
     </row>
     <row r="877">
@@ -16998,7 +16998,7 @@
       </c>
       <c r="B925" t="inlineStr">
         <is>
-          <t>General Zaragoza</t>
+          <t>Gral. Zaragoza</t>
         </is>
       </c>
       <c r="C925">
@@ -17239,7 +17239,7 @@
         <v>24</v>
       </c>
       <c r="D938">
-        <v>9.921947347532743E-05</v>
+        <v>9.921947347532744E-05</v>
       </c>
     </row>
     <row r="939">
@@ -20281,7 +20281,7 @@
         <v>24</v>
       </c>
       <c r="D1107">
-        <v>9.921947347532743E-05</v>
+        <v>9.921947347532744E-05</v>
       </c>
     </row>
     <row r="1108">
@@ -20994,7 +20994,7 @@
       </c>
       <c r="B1147" t="inlineStr">
         <is>
-          <t>San Juan Mixtepec - Distr. 08 -</t>
+          <t>San Juan Mixtepec -Dto. 08 -</t>
         </is>
       </c>
       <c r="C1147">
@@ -21012,7 +21012,7 @@
       </c>
       <c r="B1148" t="inlineStr">
         <is>
-          <t>San Juan Mixtepec - Distr. 26 -</t>
+          <t>San Juan Mixtepec -Dto. 26 -</t>
         </is>
       </c>
       <c r="C1148">
@@ -22819,7 +22819,7 @@
         <v>24</v>
       </c>
       <c r="D1248">
-        <v>9.921947347532743E-05</v>
+        <v>9.921947347532744E-05</v>
       </c>
     </row>
     <row r="1249">
@@ -22866,7 +22866,7 @@
       </c>
       <c r="B1251" t="inlineStr">
         <is>
-          <t>San Pedro Mixtepec - Distr. 22 -</t>
+          <t>San Pedro Mixtepec -Dto. 22 -</t>
         </is>
       </c>
       <c r="C1251">
@@ -22884,7 +22884,7 @@
       </c>
       <c r="B1252" t="inlineStr">
         <is>
-          <t>San Pedro Mixtepec - Distr. 26 -</t>
+          <t>San Pedro Mixtepec -Dto. 26 -</t>
         </is>
       </c>
       <c r="C1252">
@@ -23118,7 +23118,7 @@
       </c>
       <c r="B1265" t="inlineStr">
         <is>
-          <t>San Pedro Totolapa</t>
+          <t>San Pedro Totolapam</t>
         </is>
       </c>
       <c r="C1265">
@@ -23953,7 +23953,7 @@
         <v>24</v>
       </c>
       <c r="D1311">
-        <v>9.921947347532743E-05</v>
+        <v>9.921947347532744E-05</v>
       </c>
     </row>
     <row r="1312">
@@ -24187,7 +24187,7 @@
         <v>24</v>
       </c>
       <c r="D1324">
-        <v>9.921947347532743E-05</v>
+        <v>9.921947347532744E-05</v>
       </c>
     </row>
     <row r="1325">
@@ -25213,7 +25213,7 @@
         <v>24</v>
       </c>
       <c r="D1381">
-        <v>9.921947347532743E-05</v>
+        <v>9.921947347532744E-05</v>
       </c>
     </row>
     <row r="1382">
@@ -25375,7 +25375,7 @@
         <v>230</v>
       </c>
       <c r="D1390">
-        <v>0.0009508532874718879</v>
+        <v>0.000950853287471888</v>
       </c>
     </row>
     <row r="1391">
@@ -26239,7 +26239,7 @@
         <v>232</v>
       </c>
       <c r="D1438">
-        <v>0.0009591215769281651</v>
+        <v>0.0009591215769281652</v>
       </c>
     </row>
     <row r="1439">
@@ -26250,7 +26250,7 @@
       </c>
       <c r="B1439" t="inlineStr">
         <is>
-          <t>Santo Domingo Tonaltepec</t>
+          <t>Santo Domingo Tomaltepec</t>
         </is>
       </c>
       <c r="C1439">
@@ -27175,7 +27175,7 @@
         <v>227</v>
       </c>
       <c r="D1490">
-        <v>0.0009384508532874719</v>
+        <v>0.000938450853287472</v>
       </c>
     </row>
     <row r="1491">
@@ -27913,7 +27913,7 @@
         <v>24</v>
       </c>
       <c r="D1531">
-        <v>9.921947347532743E-05</v>
+        <v>9.921947347532744E-05</v>
       </c>
     </row>
     <row r="1532">
@@ -28903,7 +28903,7 @@
         <v>24</v>
       </c>
       <c r="D1586">
-        <v>9.921947347532743E-05</v>
+        <v>9.921947347532744E-05</v>
       </c>
     </row>
     <row r="1587">
@@ -29569,7 +29569,7 @@
         <v>24</v>
       </c>
       <c r="D1623">
-        <v>9.921947347532743E-05</v>
+        <v>9.921947347532744E-05</v>
       </c>
     </row>
     <row r="1624">
@@ -32647,7 +32647,7 @@
         <v>233</v>
       </c>
       <c r="D1794">
-        <v>0.0009632557216563037</v>
+        <v>0.0009632557216563036</v>
       </c>
     </row>
     <row r="1795">
@@ -34105,7 +34105,7 @@
         <v>24</v>
       </c>
       <c r="D1875">
-        <v>9.921947347532743E-05</v>
+        <v>9.921947347532744E-05</v>
       </c>
     </row>
     <row r="1876">
@@ -34969,7 +34969,7 @@
         <v>241</v>
       </c>
       <c r="D1923">
-        <v>0.0009963288794814129</v>
+        <v>0.0009963288794814127</v>
       </c>
     </row>
     <row r="1924">
@@ -35826,7 +35826,7 @@
       </c>
       <c r="B1971" t="inlineStr">
         <is>
-          <t>Ziltlaltepec De Trinidad Sanchez Santos</t>
+          <t>Zitlaltepec De Trinidad Sanchez Santos</t>
         </is>
       </c>
       <c r="C1971">
@@ -36391,7 +36391,7 @@
         <v>24</v>
       </c>
       <c r="D2002">
-        <v>9.921947347532743E-05</v>
+        <v>9.921947347532744E-05</v>
       </c>
     </row>
     <row r="2003">
@@ -37075,7 +37075,7 @@
         <v>24</v>
       </c>
       <c r="D2040">
-        <v>9.921947347532743E-05</v>
+        <v>9.921947347532744E-05</v>
       </c>
     </row>
     <row r="2041">
@@ -37129,7 +37129,7 @@
         <v>24</v>
       </c>
       <c r="D2043">
-        <v>9.921947347532743E-05</v>
+        <v>9.921947347532744E-05</v>
       </c>
     </row>
     <row r="2044">
@@ -38767,7 +38767,7 @@
         <v>24</v>
       </c>
       <c r="D2134">
-        <v>9.921947347532743E-05</v>
+        <v>9.921947347532744E-05</v>
       </c>
     </row>
     <row r="2135">
@@ -39469,7 +39469,7 @@
         <v>24</v>
       </c>
       <c r="D2173">
-        <v>9.921947347532743E-05</v>
+        <v>9.921947347532744E-05</v>
       </c>
     </row>
     <row r="2174">
@@ -39703,7 +39703,7 @@
         <v>24</v>
       </c>
       <c r="D2186">
-        <v>9.921947347532743E-05</v>
+        <v>9.921947347532744E-05</v>
       </c>
     </row>
     <row r="2187">
@@ -42007,7 +42007,7 @@
         <v>24</v>
       </c>
       <c r="D2314">
-        <v>9.921947347532743E-05</v>
+        <v>9.921947347532744E-05</v>
       </c>
     </row>
     <row r="2315">
